--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,8 +18,25 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -323,7 +340,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -331,9 +348,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Item</t>
   </si>
@@ -31,6 +31,24 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>KV-N24DR</t>
+  </si>
+  <si>
+    <t>ET-90</t>
+  </si>
+  <si>
+    <t>ET-308</t>
+  </si>
+  <si>
+    <t>KEYENCE</t>
+  </si>
+  <si>
+    <t>KV-112M</t>
+  </si>
+  <si>
+    <t>KV-108M</t>
   </si>
 </sst>
 </file>
@@ -340,7 +358,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -348,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -371,6 +389,46 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>Item</t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>KV-108M</t>
+  </si>
+  <si>
+    <t>ET-305</t>
+  </si>
+  <si>
+    <t>Blue Wire</t>
+  </si>
+  <si>
+    <t>SANWA</t>
+  </si>
+  <si>
+    <t>10 Core wire Cable (1roll)</t>
+  </si>
+  <si>
+    <t>4 Core Power Cable (1roll)</t>
+  </si>
+  <si>
+    <t>Circuit Breaker (6Amp)</t>
+  </si>
+  <si>
+    <t>Circuit Breaker (10Amp)</t>
   </si>
 </sst>
 </file>
@@ -358,7 +379,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -366,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -429,6 +450,72 @@
         <v>7</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Item</t>
   </si>
@@ -70,6 +70,33 @@
   </si>
   <si>
     <t>Circuit Breaker (10Amp)</t>
+  </si>
+  <si>
+    <t>KV-8000</t>
+  </si>
+  <si>
+    <t>SY5220-5LZE-C6</t>
+  </si>
+  <si>
+    <t>SMC</t>
+  </si>
+  <si>
+    <t>SY5120-5LZE-C6</t>
+  </si>
+  <si>
+    <t>SY5320-5LZE-C6</t>
+  </si>
+  <si>
+    <t>SY5000-26-20A (BLANKING PLATE ASSY)</t>
+  </si>
+  <si>
+    <t>SS5Y5-20-03 (MANIFOLD BASE)</t>
+  </si>
+  <si>
+    <t>KQ2H08-00A</t>
+  </si>
+  <si>
+    <t>AS1002F-06</t>
   </si>
 </sst>
 </file>
@@ -379,7 +406,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -387,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -425,6 +452,9 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
+      <c r="D3">
+        <v>374.48</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -433,6 +463,9 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
+      <c r="D4">
+        <v>462</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -460,59 +493,147 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>200.1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>60</v>
+        <v>149.30000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>228.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>223.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="D12">
+      <c r="D20">
         <v>80</v>
       </c>
     </row>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="164">
   <si>
     <t>Item</t>
   </si>
@@ -45,9 +45,6 @@
     <t>KEYENCE</t>
   </si>
   <si>
-    <t>KV-112M</t>
-  </si>
-  <si>
     <t>KV-108M</t>
   </si>
   <si>
@@ -66,12 +63,6 @@
     <t>4 Core Power Cable (1roll)</t>
   </si>
   <si>
-    <t>Circuit Breaker (6Amp)</t>
-  </si>
-  <si>
-    <t>Circuit Breaker (10Amp)</t>
-  </si>
-  <si>
     <t>KV-8000</t>
   </si>
   <si>
@@ -97,6 +88,429 @@
   </si>
   <si>
     <t>AS1002F-06</t>
+  </si>
+  <si>
+    <t>Double Hole Button Control Box</t>
+  </si>
+  <si>
+    <t>Single Hole Buton Control Box</t>
+  </si>
+  <si>
+    <t>Yellow DC Push Button</t>
+  </si>
+  <si>
+    <t>Green DC Push Button</t>
+  </si>
+  <si>
+    <t>Green DC LED</t>
+  </si>
+  <si>
+    <t>Red DC LED</t>
+  </si>
+  <si>
+    <t>White AC LED</t>
+  </si>
+  <si>
+    <t>Red Emergency Push Button</t>
+  </si>
+  <si>
+    <t>Reset Key</t>
+  </si>
+  <si>
+    <t>Iluminanted Push Button Switch</t>
+  </si>
+  <si>
+    <t>6.4A AVR</t>
+  </si>
+  <si>
+    <t>2.2A AVR</t>
+  </si>
+  <si>
+    <t>1.5A AVR</t>
+  </si>
+  <si>
+    <t>Selector Switch 2 Options</t>
+  </si>
+  <si>
+    <t>Selector Switch 3 Options</t>
+  </si>
+  <si>
+    <t>Circuit Breaker, 6Amp (KOZUKA)</t>
+  </si>
+  <si>
+    <t>Circuit Breaker, 10Amp (ABB)</t>
+  </si>
+  <si>
+    <t>Circuit Breaker, 6Amp (ABB)</t>
+  </si>
+  <si>
+    <t>Circuit Breaker, 20Amp (KOZUKA)</t>
+  </si>
+  <si>
+    <t>Magnetic Contactor (FUJI)</t>
+  </si>
+  <si>
+    <t>Magnetic Contactor (KOZUKA)</t>
+  </si>
+  <si>
+    <t>Magnetic Contactor, 18Amp (KOZUKA)</t>
+  </si>
+  <si>
+    <t>1.7A-2.6A TOR</t>
+  </si>
+  <si>
+    <t>2.2A-3.4A TOR</t>
+  </si>
+  <si>
+    <t>2.8A-4.2A TOR</t>
+  </si>
+  <si>
+    <t>Limit Switch</t>
+  </si>
+  <si>
+    <t>Relay</t>
+  </si>
+  <si>
+    <t>Block Relay</t>
+  </si>
+  <si>
+    <t>Closed End Wire Connector</t>
+  </si>
+  <si>
+    <t>Spade Terminal Y Lug</t>
+  </si>
+  <si>
+    <t>Single Terminal Block, 10Amp</t>
+  </si>
+  <si>
+    <t>Double Terminal Block, 10Amp</t>
+  </si>
+  <si>
+    <t>Buzzer</t>
+  </si>
+  <si>
+    <t>Single Metal Clad Socket</t>
+  </si>
+  <si>
+    <t>Double Metal Clad Socket</t>
+  </si>
+  <si>
+    <t>Control Box</t>
+  </si>
+  <si>
+    <t>Weatherproof Enclosed Isolator</t>
+  </si>
+  <si>
+    <t>Cable Tie</t>
+  </si>
+  <si>
+    <t>Spiral Cable Wrap</t>
+  </si>
+  <si>
+    <t>Insulation Cable Sleeving</t>
+  </si>
+  <si>
+    <t>Blue Tube Size 6</t>
+  </si>
+  <si>
+    <t>Black Tube Size 6</t>
+  </si>
+  <si>
+    <t>Black Tube Size 8</t>
+  </si>
+  <si>
+    <t>Black Tube Size 16</t>
+  </si>
+  <si>
+    <t>Oil V2</t>
+  </si>
+  <si>
+    <t>1/2" 24DCV 2/2 Way Solenoid Valve</t>
+  </si>
+  <si>
+    <t>Towerlight</t>
+  </si>
+  <si>
+    <t>Heater, 6.6Amp</t>
+  </si>
+  <si>
+    <t>Siren Buzzer</t>
+  </si>
+  <si>
+    <t>Temperature,TK4S-24RR</t>
+  </si>
+  <si>
+    <t>3 Pin Plug</t>
+  </si>
+  <si>
+    <t>PVC Insulated Cable</t>
+  </si>
+  <si>
+    <t>L Bar</t>
+  </si>
+  <si>
+    <t>Din Rail</t>
+  </si>
+  <si>
+    <t>Aluminium Box Small</t>
+  </si>
+  <si>
+    <t>FS4-IP4, 240VA (Counter)</t>
+  </si>
+  <si>
+    <t>Single Phase Motor</t>
+  </si>
+  <si>
+    <t>Black Tape</t>
+  </si>
+  <si>
+    <t>White Tape</t>
+  </si>
+  <si>
+    <t>AC Servo Motor</t>
+  </si>
+  <si>
+    <t>Test Pen</t>
+  </si>
+  <si>
+    <t>Cutter</t>
+  </si>
+  <si>
+    <t>Allen Key</t>
+  </si>
+  <si>
+    <t>Isolation Switch, TJI-3335 (35A)</t>
+  </si>
+  <si>
+    <t>Printer Tape</t>
+  </si>
+  <si>
+    <t>Battery CBP2 E03 BP2</t>
+  </si>
+  <si>
+    <t>KV-B16RC</t>
+  </si>
+  <si>
+    <t>KV-B16XC</t>
+  </si>
+  <si>
+    <t>KV-NC16EXT</t>
+  </si>
+  <si>
+    <t>KV-NC2EXT</t>
+  </si>
+  <si>
+    <t>KV-C32XTD</t>
+  </si>
+  <si>
+    <t>KV-N40DR</t>
+  </si>
+  <si>
+    <t>KV-XH04ML</t>
+  </si>
+  <si>
+    <t>KV-NC1EP</t>
+  </si>
+  <si>
+    <t>KV-N16EX</t>
+  </si>
+  <si>
+    <t>KV-N16ER</t>
+  </si>
+  <si>
+    <t>KV-7300</t>
+  </si>
+  <si>
+    <t>KV-N1</t>
+  </si>
+  <si>
+    <t>KV-EP02</t>
+  </si>
+  <si>
+    <t>KV-SH04PL</t>
+  </si>
+  <si>
+    <t>AP-C33W</t>
+  </si>
+  <si>
+    <t>EV-112M</t>
+  </si>
+  <si>
+    <t>EV-108U</t>
+  </si>
+  <si>
+    <t>EZ-18T</t>
+  </si>
+  <si>
+    <t>FU-A100</t>
+  </si>
+  <si>
+    <t>FU-R77TZ</t>
+  </si>
+  <si>
+    <t>FU-4FZ</t>
+  </si>
+  <si>
+    <t>FU-13</t>
+  </si>
+  <si>
+    <t>GL-RB01</t>
+  </si>
+  <si>
+    <t>GT-71A</t>
+  </si>
+  <si>
+    <t>IV3-H1</t>
+  </si>
+  <si>
+    <t>PZ-G</t>
+  </si>
+  <si>
+    <t>PX-G51N</t>
+  </si>
+  <si>
+    <t>PZ-G101N</t>
+  </si>
+  <si>
+    <t>SV2M010AS</t>
+  </si>
+  <si>
+    <t>AS1201F-M5-06A</t>
+  </si>
+  <si>
+    <t>AS1211F-M5-06A</t>
+  </si>
+  <si>
+    <t>AS2211F-M5-06A</t>
+  </si>
+  <si>
+    <t>IR1000-01-A (Pressure Regulator)</t>
+  </si>
+  <si>
+    <t>AN20-02 (Silencer)</t>
+  </si>
+  <si>
+    <t>IR10P-501AS (Flow Control Valve)</t>
+  </si>
+  <si>
+    <t>SS5Y5-20-05 (Manifold Base)</t>
+  </si>
+  <si>
+    <t>KQ2H06-08A</t>
+  </si>
+  <si>
+    <t>KQ2H08-10A</t>
+  </si>
+  <si>
+    <t>KQ2H10-12A</t>
+  </si>
+  <si>
+    <t>KQ2H06-00A</t>
+  </si>
+  <si>
+    <t>KQ2H10-00A</t>
+  </si>
+  <si>
+    <t>KQ2H12-00A</t>
+  </si>
+  <si>
+    <t>KQ2L06-M5A</t>
+  </si>
+  <si>
+    <t>KQ2L06-02AS</t>
+  </si>
+  <si>
+    <t>KQ2L06-03AS</t>
+  </si>
+  <si>
+    <t>KQ2S06-01AS</t>
+  </si>
+  <si>
+    <t>KQ2T04-00A</t>
+  </si>
+  <si>
+    <t>KQ2T06-00A</t>
+  </si>
+  <si>
+    <t>KQ2T08-00A</t>
+  </si>
+  <si>
+    <t>KQ2TW06-00A</t>
+  </si>
+  <si>
+    <t>KQ2U04-00A</t>
+  </si>
+  <si>
+    <t>KQ2U06-00A</t>
+  </si>
+  <si>
+    <t>KQ2U08-00A</t>
+  </si>
+  <si>
+    <t>KQ2U06-08A</t>
+  </si>
+  <si>
+    <t>KQ2V06-M5A</t>
+  </si>
+  <si>
+    <t>KQ2H10-04AS</t>
+  </si>
+  <si>
+    <t>EasyBox</t>
+  </si>
+  <si>
+    <t>CDJP2B16-40D</t>
+  </si>
+  <si>
+    <t>MKB16-10LZ</t>
+  </si>
+  <si>
+    <t>MKB16-10RZ</t>
+  </si>
+  <si>
+    <t>MKB25-10RZ</t>
+  </si>
+  <si>
+    <t>MKB12-10LZ</t>
+  </si>
+  <si>
+    <t>MKB12-10RZ</t>
+  </si>
+  <si>
+    <t>SCPD3-CB-16-15</t>
+  </si>
+  <si>
+    <t>GT-H10L</t>
+  </si>
+  <si>
+    <t>Bulb 10W, BA15S G18X30</t>
+  </si>
+  <si>
+    <t>2 Way Circuit Breaker, 10Amp (KOZUKA)</t>
+  </si>
+  <si>
+    <t>Self drill Screw</t>
+  </si>
+  <si>
+    <t>Circuit Breaker, 10Amp (KOZUKA)</t>
+  </si>
+  <si>
+    <t>MGPM20-200Z</t>
+  </si>
+  <si>
+    <t>LEY-MP32-R (Part Stacking)</t>
+  </si>
+  <si>
+    <t>LEY-MP40-R (Part Stacking EVCT)</t>
+  </si>
+  <si>
+    <t>LEFS-MP32-D (Deb Mach Slider Bawah)</t>
+  </si>
+  <si>
+    <t>LE-P56-MA-01-23 (Instocker)</t>
+  </si>
+  <si>
+    <t>LE-P56-LA-20-23(EVCT Brushing)</t>
   </si>
 </sst>
 </file>
@@ -406,7 +820,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -414,10 +828,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
@@ -444,6 +858,9 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -452,6 +869,9 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3">
         <v>374.48</v>
       </c>
@@ -463,6 +883,9 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
         <v>462</v>
       </c>
@@ -474,167 +897,1802 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>3650</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="D8">
-        <v>3650</v>
+      <c r="C8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>200.1</v>
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>149.30000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12">
-        <v>228.1</v>
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>7.06</v>
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14">
-        <v>223.95</v>
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15">
-        <v>143.5</v>
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>230.83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>149.30000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>228.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>74.650000000000006</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>16.329999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>150.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>280.52999999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>1033.1600000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>612.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>161</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>163</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>24</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>27</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>36</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>155</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>41</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>44</v>
+      </c>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>46</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>47</v>
+      </c>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>49</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>51</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>52</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>53</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>54</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>55</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>57</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>58</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>59</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>60</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>61</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>62</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>63</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>64</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>65</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>66</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>67</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>68</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>70</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>71</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>72</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>73</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>75</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>76</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>77</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>78</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>79</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>80</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>81</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>82</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>83</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>84</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>85</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>88</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>156</v>
+      </c>
+      <c r="D158">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="164">
   <si>
     <t>Item</t>
   </si>
@@ -820,7 +820,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -828,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
@@ -853,32 +853,32 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3650</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
         <v>0</v>
-      </c>
-      <c r="D3">
-        <v>374.48</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -887,23 +887,26 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>462</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
         <v>0</v>
+      </c>
+      <c r="D5">
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -912,45 +915,54 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>3650</v>
+        <v>374.48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7">
         <v>0</v>
+      </c>
+      <c r="D7">
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
         <v>0</v>
+      </c>
+      <c r="D8">
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
         <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3650</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -961,7 +973,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -972,7 +984,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -983,7 +995,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -994,7 +1006,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -1005,7 +1017,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -1016,183 +1028,195 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>100</v>
       </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>101</v>
       </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>102</v>
       </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>103</v>
       </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>338.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>117.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>105</v>
       </c>
-      <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>202.86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>106</v>
       </c>
-      <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>192.28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>107</v>
       </c>
-      <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>108</v>
       </c>
-      <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>110</v>
       </c>
-      <c r="B29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>111</v>
       </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>112</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>153</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -1203,7 +1227,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -1214,7 +1238,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -1225,7 +1249,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -1236,43 +1260,46 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
       </c>
       <c r="C36">
         <v>0</v>
+      </c>
+      <c r="D36">
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
       </c>
       <c r="C37">
         <v>0</v>
+      </c>
+      <c r="D37">
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>0</v>
-      </c>
-      <c r="D38">
-        <v>230.83</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
@@ -1281,12 +1308,12 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>149.30000000000001</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
@@ -1295,12 +1322,12 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>228.1</v>
+        <v>149.30000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
@@ -1309,12 +1336,12 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>7.06</v>
+        <v>228.1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
@@ -1323,12 +1350,12 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>74.650000000000006</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
@@ -1337,12 +1364,12 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>143.5</v>
+        <v>74.650000000000006</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
@@ -1351,12 +1378,12 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>170</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
         <v>16</v>
@@ -1365,12 +1392,12 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>16.23</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
@@ -1379,23 +1406,26 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>16.329999999999998</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47">
         <v>0</v>
+      </c>
+      <c r="D47">
+        <v>16.329999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
@@ -1406,7 +1436,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
@@ -1417,7 +1447,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
@@ -1428,32 +1458,32 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51">
         <v>0</v>
-      </c>
-      <c r="D51">
-        <v>150.1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52">
         <v>0</v>
+      </c>
+      <c r="D52">
+        <v>150.1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
@@ -1464,21 +1494,18 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
         <v>16</v>
       </c>
       <c r="C54">
         <v>0</v>
-      </c>
-      <c r="D54">
-        <v>8.01</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
@@ -1487,23 +1514,26 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
         <v>16</v>
       </c>
       <c r="C56">
         <v>0</v>
+      </c>
+      <c r="D56">
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
@@ -1514,7 +1544,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
@@ -1525,7 +1555,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
@@ -1536,7 +1566,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
@@ -1547,7 +1577,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
@@ -1558,7 +1588,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
@@ -1569,7 +1599,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
@@ -1580,7 +1610,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
@@ -1591,7 +1621,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
@@ -1602,7 +1632,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
@@ -1613,7 +1643,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
         <v>16</v>
@@ -1624,7 +1654,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s">
         <v>16</v>
@@ -1635,7 +1665,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
         <v>16</v>
@@ -1646,7 +1676,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
@@ -1657,7 +1687,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
         <v>16</v>
@@ -1668,7 +1698,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
@@ -1679,7 +1709,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
@@ -1690,7 +1720,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
         <v>16</v>
@@ -1701,7 +1731,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
         <v>16</v>
@@ -1712,7 +1742,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
         <v>16</v>
@@ -1723,7 +1753,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
         <v>16</v>
@@ -1734,7 +1764,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B78" t="s">
         <v>16</v>
@@ -1745,21 +1775,18 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
         <v>16</v>
       </c>
       <c r="C79">
         <v>0</v>
-      </c>
-      <c r="D79">
-        <v>280.52999999999997</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
         <v>16</v>
@@ -1768,12 +1795,12 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1033.1600000000001</v>
+        <v>280.52999999999997</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
         <v>16</v>
@@ -1782,23 +1809,26 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>612.6</v>
+        <v>1033.1600000000001</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
       </c>
       <c r="C82">
         <v>0</v>
+      </c>
+      <c r="D82">
+        <v>612.6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
         <v>16</v>
@@ -1809,7 +1839,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
         <v>16</v>
@@ -1820,7 +1850,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
         <v>16</v>
@@ -1831,21 +1861,18 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C86">
         <v>0</v>
-      </c>
-      <c r="D86">
-        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
@@ -1854,12 +1881,12 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>700</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
@@ -1868,12 +1895,12 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
@@ -1882,12 +1909,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>60</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
@@ -1896,12 +1923,12 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
@@ -1910,23 +1937,26 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92">
         <v>0</v>
+      </c>
+      <c r="D92">
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
@@ -1937,32 +1967,32 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
         <v>11</v>
       </c>
       <c r="C94">
         <v>0</v>
-      </c>
-      <c r="D94">
-        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B95" t="s">
         <v>11</v>
       </c>
       <c r="C95">
         <v>0</v>
+      </c>
+      <c r="D95">
+        <v>110</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
         <v>11</v>
@@ -1973,7 +2003,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B97" t="s">
         <v>11</v>
@@ -1984,7 +2014,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
@@ -1995,7 +2025,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -2006,7 +2036,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
         <v>11</v>
@@ -2017,21 +2047,18 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
         <v>11</v>
       </c>
       <c r="C101">
         <v>0</v>
-      </c>
-      <c r="D101">
-        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
         <v>11</v>
@@ -2040,12 +2067,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>120</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
         <v>11</v>
@@ -2054,23 +2081,26 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B104" t="s">
         <v>11</v>
       </c>
       <c r="C104">
         <v>0</v>
+      </c>
+      <c r="D104">
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
         <v>11</v>
@@ -2081,82 +2111,82 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="B106" t="s">
         <v>11</v>
       </c>
       <c r="C106">
         <v>0</v>
-      </c>
-      <c r="D106">
-        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="B107" t="s">
         <v>11</v>
       </c>
       <c r="C107">
         <v>0</v>
+      </c>
+      <c r="D107">
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="B108" t="s">
         <v>11</v>
       </c>
       <c r="C108">
         <v>0</v>
-      </c>
-      <c r="D108">
-        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="B109" t="s">
         <v>11</v>
       </c>
       <c r="C109">
         <v>0</v>
+      </c>
+      <c r="D109">
+        <v>70</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B110" t="s">
         <v>11</v>
       </c>
       <c r="C110">
         <v>0</v>
-      </c>
-      <c r="D110">
-        <v>130</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B111" t="s">
         <v>11</v>
       </c>
       <c r="C111">
         <v>0</v>
+      </c>
+      <c r="D111">
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B112" t="s">
         <v>11</v>
@@ -2167,21 +2197,18 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B113" t="s">
         <v>11</v>
       </c>
       <c r="C113">
         <v>0</v>
-      </c>
-      <c r="D113">
-        <v>95</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
         <v>11</v>
@@ -2195,7 +2222,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B115" t="s">
         <v>11</v>
@@ -2209,18 +2236,21 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B116" t="s">
         <v>11</v>
       </c>
       <c r="C116">
         <v>0</v>
+      </c>
+      <c r="D116">
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B117" t="s">
         <v>11</v>
@@ -2231,7 +2261,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B118" t="s">
         <v>11</v>
@@ -2242,7 +2272,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B119" t="s">
         <v>11</v>
@@ -2253,7 +2283,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B120" t="s">
         <v>11</v>
@@ -2264,7 +2294,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B121" t="s">
         <v>11</v>
@@ -2275,7 +2305,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B122" t="s">
         <v>11</v>
@@ -2286,7 +2316,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B123" t="s">
         <v>11</v>
@@ -2297,7 +2327,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B124" t="s">
         <v>11</v>
@@ -2308,7 +2338,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B125" t="s">
         <v>11</v>
@@ -2319,7 +2349,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B126" t="s">
         <v>11</v>
@@ -2330,21 +2360,18 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B127" t="s">
         <v>11</v>
       </c>
       <c r="C127">
         <v>0</v>
-      </c>
-      <c r="D127">
-        <v>50</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B128" t="s">
         <v>11</v>
@@ -2353,23 +2380,26 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B129" t="s">
         <v>11</v>
       </c>
       <c r="C129">
         <v>0</v>
+      </c>
+      <c r="D129">
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B130" t="s">
         <v>11</v>
@@ -2380,7 +2410,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B131" t="s">
         <v>11</v>
@@ -2391,7 +2421,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B132" t="s">
         <v>11</v>
@@ -2402,7 +2432,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B133" t="s">
         <v>11</v>
@@ -2413,46 +2443,43 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B134" t="s">
         <v>11</v>
       </c>
       <c r="C134">
         <v>0</v>
-      </c>
-      <c r="D134">
-        <v>980</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B135" t="s">
         <v>11</v>
       </c>
       <c r="C135">
         <v>0</v>
+      </c>
+      <c r="D135">
+        <v>980</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B136" t="s">
         <v>11</v>
       </c>
       <c r="C136">
         <v>0</v>
-      </c>
-      <c r="D136">
-        <v>280</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B137" t="s">
         <v>11</v>
@@ -2461,23 +2488,26 @@
         <v>0</v>
       </c>
       <c r="D137">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B138" t="s">
         <v>11</v>
       </c>
       <c r="C138">
         <v>0</v>
+      </c>
+      <c r="D138">
+        <v>230</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B139" t="s">
         <v>11</v>
@@ -2488,7 +2518,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
         <v>11</v>
@@ -2499,7 +2529,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s">
         <v>11</v>
@@ -2510,7 +2540,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B142" t="s">
         <v>11</v>
@@ -2521,7 +2551,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B143" t="s">
         <v>11</v>
@@ -2532,7 +2562,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B144" t="s">
         <v>11</v>
@@ -2543,7 +2573,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B145" t="s">
         <v>11</v>
@@ -2554,7 +2584,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B146" t="s">
         <v>11</v>
@@ -2565,7 +2595,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B147" t="s">
         <v>11</v>
@@ -2576,7 +2606,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B148" t="s">
         <v>11</v>
@@ -2587,7 +2617,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B149" t="s">
         <v>11</v>
@@ -2598,7 +2628,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B150" t="s">
         <v>11</v>
@@ -2609,32 +2639,32 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="B151" t="s">
         <v>11</v>
       </c>
       <c r="C151">
         <v>0</v>
-      </c>
-      <c r="D151">
-        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="B152" t="s">
         <v>11</v>
       </c>
       <c r="C152">
         <v>0</v>
+      </c>
+      <c r="D152">
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B153" t="s">
         <v>11</v>
@@ -2645,7 +2675,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B154" t="s">
         <v>11</v>
@@ -2656,7 +2686,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B155" t="s">
         <v>11</v>
@@ -2667,7 +2697,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B156" t="s">
         <v>11</v>
@@ -2678,7 +2708,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B157" t="s">
         <v>11</v>
@@ -2689,9 +2719,26 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>88</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>156</v>
       </c>
-      <c r="D158">
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
         <v>45</v>
       </c>
     </row>
